--- a/artfynd/A 23035-2022 artfynd.xlsx
+++ b/artfynd/A 23035-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23035-2022 artfynd.xlsx
+++ b/artfynd/A 23035-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94067073</v>
+        <v>102942288</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +686,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kullabäcken, Vb</t>
+          <t>Tjälamark, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754651.8582462484</v>
+        <v>754884</v>
       </c>
       <c r="R2" t="n">
-        <v>7094622.943443998</v>
+        <v>7094724</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-06-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>18:10</t>
+          <t>2022-08-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-06-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>18:10</t>
+          <t>2022-08-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,38 +771,33 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Blandskog i branter</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Persson</t>
+          <t>Andreas Estensen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Persson, Andreas Estensen, Emma Johansson</t>
+          <t>Andreas Estensen, Tonje Lindmark, Carl Jansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 23035-2022 artfynd.xlsx
+++ b/artfynd/A 23035-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -801,8 +806,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102942288</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>